--- a/db_schema.xlsx
+++ b/db_schema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa-Slayer\Desktop\Staj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa-Slayer\Desktop\TRADEHUB_FLUTTER_NEXT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1ABD82-6DA6-409A-AAD3-D41E3E8DF69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93A2609-3FD9-4651-A53C-2D910A78CE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="161">
   <si>
     <t>USERS</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>VARCHAR(600)</t>
+  </si>
+  <si>
+    <t>FAVORITES</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,6 +648,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -658,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -723,6 +732,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1439,7 +1454,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1817,9 +1832,11 @@
       <c r="L24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N24" s="13"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="13"/>
+      <c r="N24" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
@@ -1827,7 +1844,7 @@
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="24" t="s">
         <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -1845,9 +1862,15 @@
       <c r="L25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
+      <c r="N25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1876,6 +1899,15 @@
       </c>
       <c r="L26" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1897,6 +1929,15 @@
       <c r="G27" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="N27" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
@@ -1922,6 +1963,15 @@
       </c>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
+      <c r="N28" t="s">
+        <v>115</v>
+      </c>
+      <c r="O28" t="s">
+        <v>130</v>
+      </c>
+      <c r="P28" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
@@ -1942,6 +1992,15 @@
       <c r="L29" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="N29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
@@ -1962,6 +2021,15 @@
       <c r="L30" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="N30" t="s">
+        <v>117</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
@@ -1993,7 +2061,7 @@
       <c r="C32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="24" t="s">
         <v>91</v>
       </c>
       <c r="K32" s="2" t="s">
@@ -2037,7 +2105,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="J15:L15"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="J5:L5"/>
@@ -2045,13 +2119,8 @@
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="E22:G22"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="N24:P24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/db_schema.xlsx
+++ b/db_schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa-Slayer\Desktop\TRADEHUB_FLUTTER_NEXT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93A2609-3FD9-4651-A53C-2D910A78CE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDEE901-F5B1-44DE-B432-C874189480BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="167">
   <si>
     <t>USERS</t>
   </si>
@@ -503,6 +503,24 @@
   </si>
   <si>
     <t>FAVORITES</t>
+  </si>
+  <si>
+    <t>REVIEWS</t>
+  </si>
+  <si>
+    <t>RATING</t>
+  </si>
+  <si>
+    <t>COMMENT</t>
+  </si>
+  <si>
+    <t>PUAN</t>
+  </si>
+  <si>
+    <t>YORUM</t>
+  </si>
+  <si>
+    <t>VARCHAR(800)</t>
   </si>
 </sst>
 </file>
@@ -726,18 +744,18 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1063,26 +1081,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="J1" s="20" t="s">
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="J1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="N1" s="20" t="s">
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="N1" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1208,11 +1226,11 @@
       <c r="G5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
       <c r="N5" s="13" t="s">
         <v>88</v>
       </c>
@@ -1376,11 +1394,11 @@
       <c r="C10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
       <c r="N10" s="13" t="s">
         <v>115</v>
       </c>
@@ -1395,11 +1413,11 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
       <c r="J11" s="8" t="s">
         <v>3</v>
       </c>
@@ -1420,11 +1438,11 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="9" t="s">
         <v>3</v>
       </c>
@@ -1454,7 +1472,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1501,11 +1519,11 @@
       <c r="G14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="22" t="s">
+      <c r="N14" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -1526,11 +1544,11 @@
       <c r="G15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
       <c r="N15" s="18" t="s">
         <v>3</v>
       </c>
@@ -1703,11 +1721,11 @@
       <c r="G20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
       <c r="N20" s="13" t="s">
         <v>137</v>
       </c>
@@ -1757,11 +1775,11 @@
       <c r="C22" t="s">
         <v>159</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
       <c r="J22" s="9" t="s">
         <v>74</v>
       </c>
@@ -1832,19 +1850,19 @@
       <c r="L24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N24" s="20" t="s">
+      <c r="N24" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="E25" s="24" t="s">
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="E25" s="21" t="s">
         <v>91</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -1929,7 +1947,7 @@
       <c r="G27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N27" s="23" t="s">
+      <c r="N27" s="20" t="s">
         <v>91</v>
       </c>
       <c r="O27" s="2" t="s">
@@ -1958,11 +1976,11 @@
       <c r="G28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
       <c r="N28" t="s">
         <v>115</v>
       </c>
@@ -2061,7 +2079,7 @@
       <c r="C32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J32" s="24" t="s">
+      <c r="J32" s="21" t="s">
         <v>91</v>
       </c>
       <c r="K32" s="2" t="s">
@@ -2070,8 +2088,13 @@
       <c r="L32" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="N32" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+    </row>
+    <row r="33" spans="10:16" x14ac:dyDescent="0.25">
       <c r="J33" s="2" t="s">
         <v>94</v>
       </c>
@@ -2081,8 +2104,17 @@
       <c r="L33" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="N33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="10:16" x14ac:dyDescent="0.25">
       <c r="J34" s="2" t="s">
         <v>65</v>
       </c>
@@ -2092,8 +2124,17 @@
       <c r="L34" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="N34" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="10:16" x14ac:dyDescent="0.25">
       <c r="J35" s="2" t="s">
         <v>100</v>
       </c>
@@ -2103,15 +2144,85 @@
       <c r="L35" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="N35" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N36" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N37" t="s">
+        <v>162</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N38" t="s">
+        <v>163</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N39" t="s">
+        <v>115</v>
+      </c>
+      <c r="O39" t="s">
+        <v>130</v>
+      </c>
+      <c r="P39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N40" t="s">
+        <v>116</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="N41" t="s">
+        <v>117</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="J15:L15"/>
+  <mergeCells count="16">
+    <mergeCell ref="N32:P32"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="J5:L5"/>
@@ -2121,6 +2232,12 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="N24:P24"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="J15:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
